--- a/templates/gabarit_officiel.xlsx
+++ b/templates/gabarit_officiel.xlsx
@@ -737,7 +737,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId186"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId187"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -778,7 +778,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId187"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId188"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -819,7 +819,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId188"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId189"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -860,7 +860,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId189"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId190"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -901,7 +901,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId190"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId191"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -942,7 +942,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId191"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId192"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -983,7 +983,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId192"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId193"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1024,7 +1024,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId193"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId194"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1065,7 +1065,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId194"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId195"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1106,7 +1106,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId195"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId196"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1147,7 +1147,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId196"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId197"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1188,7 +1188,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId197"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId198"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1229,7 +1229,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId198"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId199"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1270,7 +1270,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId199"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId200"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1311,7 +1311,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId200"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId201"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1352,7 +1352,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId201"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId202"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1393,7 +1393,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId202"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId203"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1434,7 +1434,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId203"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId204"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1475,7 +1475,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId204"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId205"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1516,7 +1516,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId205"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId206"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1557,7 +1557,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId206"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId207"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1598,7 +1598,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId207"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId208"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1639,7 +1639,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId208"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId209"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1680,7 +1680,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId209"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId210"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1721,7 +1721,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId210"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId211"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1762,7 +1762,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId211"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId212"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1803,7 +1803,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId212"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId213"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1844,7 +1844,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId213"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId214"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1885,7 +1885,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId214"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId215"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1905,6 +1905,47 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>83</col>
+      <colOff>123265</colOff>
+      <row>0</row>
+      <rowOff>67236</rowOff>
+    </from>
+    <to>
+      <col>83</col>
+      <colOff>392207</colOff>
+      <row>1</row>
+      <rowOff>510935</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 28"/>
+        <cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId216"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="64613118" y="257736"/>
+          <a:ext cx="268942" cy="443699"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -4254,9 +4295,9 @@
   <oneCellAnchor>
     <from>
       <col>83</col>
-      <colOff>261938</colOff>
-      <row>0</row>
-      <rowOff>147638</rowOff>
+      <colOff>519673</colOff>
+      <row>0</row>
+      <rowOff>170049</rowOff>
     </from>
     <ext cx="238125" cy="238125"/>
     <pic>
@@ -4272,7 +4313,7 @@
       </blipFill>
       <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="64746188" y="338138"/>
+          <a:off x="65009526" y="360549"/>
           <a:ext cx="238125" cy="238125"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
@@ -6770,9 +6811,9 @@
   <oneCellAnchor>
     <from>
       <col>178</col>
-      <colOff>261938</colOff>
-      <row>0</row>
-      <rowOff>147638</rowOff>
+      <colOff>463644</colOff>
+      <row>0</row>
+      <rowOff>192463</rowOff>
     </from>
     <ext cx="238125" cy="238125"/>
     <pic>
@@ -6788,7 +6829,7 @@
       </blipFill>
       <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="137336213" y="338138"/>
+          <a:off x="137959820" y="382963"/>
           <a:ext cx="238125" cy="238125"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
@@ -8192,6 +8233,42 @@
           <avLst/>
         </a:prstGeom>
         <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>178</col>
+      <colOff>134471</colOff>
+      <row>0</row>
+      <rowOff>156882</rowOff>
+    </from>
+    <ext cx="314369" cy="266737"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 30"/>
+        <cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId186"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="137630647" y="347382"/>
+          <a:ext cx="314369" cy="266737"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>

--- a/templates/gabarit_officiel.xlsx
+++ b/templates/gabarit_officiel.xlsx
@@ -362,7 +362,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -385,11 +385,55 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="47" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -638,6 +682,17 @@
     <xf numFmtId="0" fontId="2" fillId="52" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="47" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8581,28 +8636,61 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="HM1" s="1" t="inlineStr">
+      <c r="HM1" s="86" t="inlineStr">
         <is>
           <t>GEORISQUE</t>
         </is>
       </c>
-      <c r="MM1" s="2" t="inlineStr">
+      <c r="MM1" s="87" t="inlineStr">
         <is>
           <t>Plans de prévention des risques
 (PPR-Commune)</t>
         </is>
       </c>
-      <c r="NI1" s="3" t="inlineStr">
+      <c r="MN1" s="88" t="n"/>
+      <c r="MO1" s="88" t="n"/>
+      <c r="MP1" s="88" t="n"/>
+      <c r="MQ1" s="88" t="n"/>
+      <c r="MR1" s="88" t="n"/>
+      <c r="MS1" s="88" t="n"/>
+      <c r="MT1" s="88" t="n"/>
+      <c r="MU1" s="88" t="n"/>
+      <c r="MV1" s="88" t="n"/>
+      <c r="MW1" s="88" t="n"/>
+      <c r="MX1" s="88" t="n"/>
+      <c r="MY1" s="88" t="n"/>
+      <c r="MZ1" s="88" t="n"/>
+      <c r="NA1" s="88" t="n"/>
+      <c r="NB1" s="88" t="n"/>
+      <c r="NC1" s="88" t="n"/>
+      <c r="ND1" s="88" t="n"/>
+      <c r="NE1" s="88" t="n"/>
+      <c r="NF1" s="88" t="n"/>
+      <c r="NG1" s="88" t="n"/>
+      <c r="NH1" s="89" t="n"/>
+      <c r="NI1" s="56" t="inlineStr">
         <is>
           <t>Plans de prévention des risques
 (Servitudes d'utilité publique SUP)</t>
         </is>
       </c>
-      <c r="NW1" s="4" t="inlineStr">
+      <c r="NJ1" s="88" t="n"/>
+      <c r="NK1" s="88" t="n"/>
+      <c r="NL1" s="88" t="n"/>
+      <c r="NM1" s="88" t="n"/>
+      <c r="NN1" s="88" t="n"/>
+      <c r="NO1" s="88" t="n"/>
+      <c r="NP1" s="89" t="n"/>
+      <c r="NW1" s="90" t="inlineStr">
         <is>
           <t>Sites et sols (Potentiellement) pollués</t>
         </is>
       </c>
+      <c r="NX1" s="88" t="n"/>
+      <c r="NY1" s="88" t="n"/>
+      <c r="NZ1" s="88" t="n"/>
+      <c r="OA1" s="88" t="n"/>
+      <c r="OB1" s="89" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -11603,6 +11691,11 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="NI1:NP1"/>
+    <mergeCell ref="MM1:NH1"/>
+    <mergeCell ref="NW1:OB1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
